--- a/docs/dummy/아동등록_샘플.xlsx
+++ b/docs/dummy/아동등록_샘플.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H13"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="12.83203125" customWidth="1"/>
@@ -443,7 +443,7 @@
         <v>2019.03.05</v>
       </c>
       <c r="C2" t="str">
-        <v>10:00~10:50</v>
+        <v>09:00~09:50</v>
       </c>
       <c r="D2" t="str">
         <v>월, 수</v>
@@ -469,7 +469,7 @@
         <v>2020.07.21</v>
       </c>
       <c r="C3" t="str">
-        <v>13:30~14:20</v>
+        <v>09:00~09:50</v>
       </c>
       <c r="D3" t="str">
         <v>화, 목</v>
@@ -495,7 +495,7 @@
         <v>2018.11.02</v>
       </c>
       <c r="C4" t="str">
-        <v>15:10~16:00</v>
+        <v>09:50~10:40</v>
       </c>
       <c r="D4" t="str">
         <v>월, 금</v>
@@ -521,7 +521,7 @@
         <v>2021.01.15</v>
       </c>
       <c r="C5" t="str">
-        <v>11:30~12:20</v>
+        <v>10:40~11:30</v>
       </c>
       <c r="D5" t="str">
         <v>수, 금</v>
@@ -547,7 +547,7 @@
         <v>2019.09.09</v>
       </c>
       <c r="C6" t="str">
-        <v>16:00~16:50</v>
+        <v>11:30~12:20</v>
       </c>
       <c r="D6" t="str">
         <v>화, 금</v>
@@ -565,9 +565,191 @@
         <v/>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" t="str">
+        <v>한서준</v>
+      </c>
+      <c r="B7" t="str">
+        <v>2020.02.18</v>
+      </c>
+      <c r="C7" t="str">
+        <v>10:40~11:30</v>
+      </c>
+      <c r="D7" t="str">
+        <v>월, 목</v>
+      </c>
+      <c r="E7">
+        <v>35000</v>
+      </c>
+      <c r="F7">
+        <v>40000</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="str">
+        <v>오지우</v>
+      </c>
+      <c r="B8" t="str">
+        <v>2018.06.30</v>
+      </c>
+      <c r="C8" t="str">
+        <v>09:50~10:40</v>
+      </c>
+      <c r="D8" t="str">
+        <v>화, 수</v>
+      </c>
+      <c r="E8">
+        <v>35000</v>
+      </c>
+      <c r="F8">
+        <v>60000</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="str">
+        <v>윤서아</v>
+      </c>
+      <c r="B9" t="str">
+        <v>2021.05.11</v>
+      </c>
+      <c r="C9" t="str">
+        <v>13:30~14:20</v>
+      </c>
+      <c r="D9" t="str">
+        <v>목, 금</v>
+      </c>
+      <c r="E9">
+        <v>35000</v>
+      </c>
+      <c r="F9">
+        <v>0</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="str">
+        <v>임도현</v>
+      </c>
+      <c r="B10" t="str">
+        <v>2019.12.25</v>
+      </c>
+      <c r="C10" t="str">
+        <v>13:30~14:20</v>
+      </c>
+      <c r="D10" t="str">
+        <v>월, 화</v>
+      </c>
+      <c r="E10">
+        <v>35000</v>
+      </c>
+      <c r="F10">
+        <v>40000</v>
+      </c>
+      <c r="G10">
+        <v>8</v>
+      </c>
+      <c r="H10" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
+        <v>강시우</v>
+      </c>
+      <c r="B11" t="str">
+        <v>2020.10.08</v>
+      </c>
+      <c r="C11" t="str">
+        <v>11:30~12:20</v>
+      </c>
+      <c r="D11" t="str">
+        <v>수, 목</v>
+      </c>
+      <c r="E11">
+        <v>35000</v>
+      </c>
+      <c r="F11">
+        <v>20000</v>
+      </c>
+      <c r="G11">
+        <v>8</v>
+      </c>
+      <c r="H11" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="str">
+        <v>조하린</v>
+      </c>
+      <c r="B12" t="str">
+        <v>2018.08.14</v>
+      </c>
+      <c r="C12" t="str">
+        <v>14:20~15:10</v>
+      </c>
+      <c r="D12" t="str">
+        <v>월, 수</v>
+      </c>
+      <c r="E12">
+        <v>35000</v>
+      </c>
+      <c r="F12">
+        <v>80000</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
+      </c>
+      <c r="H12" t="str">
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>배은우</v>
+      </c>
+      <c r="B13" t="str">
+        <v>2021.04.02</v>
+      </c>
+      <c r="C13" t="str">
+        <v>14:20~15:10</v>
+      </c>
+      <c r="D13" t="str">
+        <v>화, 목</v>
+      </c>
+      <c r="E13">
+        <v>35000</v>
+      </c>
+      <c r="F13">
+        <v>40000</v>
+      </c>
+      <c r="G13">
+        <v>8</v>
+      </c>
+      <c r="H13" t="str">
+        <v/>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:H6"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H13"/>
   </ignoredErrors>
 </worksheet>
 </file>